--- a/artfynd/A 37232-2021 artfynd.xlsx
+++ b/artfynd/A 37232-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>125533023</v>
       </c>
       <c r="B2" t="n">
-        <v>91459</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37232-2021 artfynd.xlsx
+++ b/artfynd/A 37232-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125533023</v>
       </c>
       <c r="B2" t="n">
-        <v>91513</v>
+        <v>91520</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37232-2021 artfynd.xlsx
+++ b/artfynd/A 37232-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125533023</v>
       </c>
       <c r="B2" t="n">
-        <v>91520</v>
+        <v>91524</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37232-2021 artfynd.xlsx
+++ b/artfynd/A 37232-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125533023</v>
       </c>
       <c r="B2" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37232-2021 artfynd.xlsx
+++ b/artfynd/A 37232-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125533023</v>
       </c>
       <c r="B2" t="n">
-        <v>91528</v>
+        <v>91530</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37232-2021 artfynd.xlsx
+++ b/artfynd/A 37232-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125533023</v>
       </c>
       <c r="B2" t="n">
-        <v>91530</v>
+        <v>91532</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37232-2021 artfynd.xlsx
+++ b/artfynd/A 37232-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125533023</v>
+        <v>125532512</v>
       </c>
       <c r="B2" t="n">
-        <v>91532</v>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590907</v>
+        <v>590948</v>
       </c>
       <c r="R2" t="n">
-        <v>6931684</v>
+        <v>6931628</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -769,6 +769,205 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>125533023</v>
+      </c>
+      <c r="B3" t="n">
+        <v>92208</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>658</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Gräsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>590907</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6931684</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125533241</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Gräsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>590862</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6931651</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sättna</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
